--- a/company-analyzer/outputs/toyota/トヨタ自動車_財務分析.xlsx
+++ b/company-analyzer/outputs/toyota/トヨタ自動車_財務分析.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="財務指標" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="損益計算書" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="貸借対照表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF計算書" sheetId="4" state="visible" r:id="rId4"/>
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
@@ -61,11 +61,6 @@
     <font>
       <sz val="9"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -433,7 +428,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -519,6 +514,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -528,7 +535,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -896,683 +902,414 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="C3:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="28" customWidth="1" style="28" min="1" max="1"/>
-    <col width="10" customWidth="1" style="28" min="2" max="2"/>
-    <col width="10" customWidth="1" style="28" min="3" max="3"/>
-    <col width="10" customWidth="1" style="28" min="4" max="4"/>
-    <col width="10" customWidth="1" style="28" min="5" max="5"/>
-    <col width="10" customWidth="1" style="28" min="6" max="6"/>
-    <col width="10" customWidth="1" style="28" min="7" max="7"/>
-    <col width="10" customWidth="1" style="28" min="8" max="8"/>
-    <col width="10" customWidth="1" style="28" min="9" max="9"/>
-    <col width="10" customWidth="1" style="28" min="10" max="10"/>
-    <col width="10" customWidth="1" style="28" min="11" max="11"/>
+    <col width="20" customWidth="1" style="28" min="3" max="3"/>
+    <col width="12.08984375" customWidth="1" style="28" min="4" max="4"/>
+    <col width="12.453125" customWidth="1" style="28" min="5" max="5"/>
+    <col width="12.26953125" customWidth="1" style="28" min="6" max="6"/>
+    <col width="13" customWidth="1" style="28" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>財務指標</t>
-        </is>
-      </c>
-      <c r="B1" s="29" t="inlineStr">
-        <is>
-          <t>2014年3月期</t>
-        </is>
-      </c>
-      <c r="C1" s="29" t="inlineStr">
-        <is>
-          <t>2015年3月期</t>
-        </is>
-      </c>
-      <c r="D1" s="29" t="inlineStr">
-        <is>
-          <t>2016年3月期</t>
-        </is>
-      </c>
-      <c r="E1" s="29" t="inlineStr">
-        <is>
-          <t>2017年3月期</t>
-        </is>
-      </c>
-      <c r="F1" s="29" t="inlineStr">
-        <is>
-          <t>2018年3月期</t>
-        </is>
-      </c>
-      <c r="G1" s="29" t="inlineStr">
+    <row r="3">
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>財務諸表分析シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" s="28" thickBot="1">
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>2019年3月期</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>2020年3月期</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>2021年3月期</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>2022年3月期</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>2023年3月期</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>総資産利益率（ROA） (%)</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="C2" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D2" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E2" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F2" s="31" t="n">
+    <row r="6" ht="22.25" customHeight="1" s="28">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1" s="28">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="8" ht="23.4" customHeight="1" s="28">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>営業利益率</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="9" ht="26.4" customHeight="1" s="28">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>自己資本比率</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="10" ht="25.9" customHeight="1" s="28">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>総資産回転率</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" ht="27.65" customHeight="1" s="28">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>インタレスト・カバレッジ</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="28">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>株価推移</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n">
+        <v>7300</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>8600</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>9200</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="13" ht="28.9" customHeight="1" s="28">
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>純資産成長率</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n">
         <v>5.2</v>
       </c>
-      <c r="G2" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H2" s="31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I2" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J2" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" s="31" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>自己資本利益率（ROE） (%)</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="n">
+      <c r="F13" s="17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H13" s="7" t="n">
         <v>14.1</v>
       </c>
-      <c r="C3" s="31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="D3" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E3" s="31" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F3" s="31" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G3" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I3" s="31" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J3" s="31" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="K3" s="31" t="n">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="4" ht="13.5" customHeight="1" s="28" thickBot="1">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>売上高営業利益率 (%)</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="C4" s="31" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="D4" s="31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E4" s="31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F4" s="31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G4" s="31" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H4" s="31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I4" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K4" s="31" t="n">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>自己資本比率 (%)</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="n">
-        <v>36</v>
-      </c>
-      <c r="C5" s="31" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="G5" s="31" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="H5" s="31" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="I5" s="31" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="J5" s="31" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="K5" s="31" t="n">
-        <v>38.6</v>
-      </c>
-    </row>
-    <row r="6" ht="22.25" customHeight="1" s="28">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>総資産回転率 (回)</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H6" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K6" s="31" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1" s="28">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>インタレスト・カバレッジ・レシオ（ICR） (倍)</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="31" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="G7" s="31" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="H7" s="31" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I7" s="31" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="J7" s="31" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="K7" s="31" t="n">
-        <v>40.2</v>
-      </c>
-    </row>
-    <row r="8" ht="23.4" customHeight="1" s="28">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>株価 (円)</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="n">
-        <v>7100</v>
-      </c>
-      <c r="C8" s="31" t="n">
-        <v>8200</v>
-      </c>
-      <c r="D8" s="31" t="n">
-        <v>6600</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F8" s="31" t="n">
-        <v>7200</v>
-      </c>
-      <c r="G8" s="31" t="n">
-        <v>7300</v>
-      </c>
-      <c r="H8" s="31" t="n">
-        <v>6800</v>
-      </c>
-      <c r="I8" s="31" t="n">
-        <v>8600</v>
-      </c>
-      <c r="J8" s="31" t="n">
-        <v>9200</v>
-      </c>
-      <c r="K8" s="31" t="n">
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="9" ht="26.4" customHeight="1" s="28">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>純資産成長率 (%)</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="31" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E9" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="F9" s="31" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="G9" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H9" s="31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I9" s="31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J9" s="31" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="K9" s="31" t="n">
+      <c r="I13" s="24" t="n">
         <v>8.300000000000001</v>
       </c>
     </row>
-    <row r="10" ht="25.9" customHeight="1" s="28">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>株価純資産倍率（PBR） (倍)</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
+    <row r="14" ht="22.9" customHeight="1" s="28" thickBot="1">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G14" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I14" s="24" t="n">
         <v>1.1</v>
       </c>
-      <c r="C10" s="31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D10" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J10" s="31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="11" ht="27.65" customHeight="1" s="28">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>減損損失 (億円)</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="n">
-        <v>320</v>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>850</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>210</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>180</v>
-      </c>
-      <c r="G11" s="31" t="n">
+    </row>
+    <row r="15" ht="21" customHeight="1" s="28">
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>セグメント別売上高</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1" s="28">
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>北米</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>アジア</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>本田なら４輪と二輪</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28.9" customHeight="1" s="28">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>減損額</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="H11" s="31" t="n">
+      <c r="F17" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="I11" s="31" t="n">
+      <c r="G17" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="H17" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="K11" s="31" t="n">
+      <c r="I17" s="24" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="28">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>商社ならグループごと</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>債券格付</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
-      <c r="D12" s="31" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
-      <c r="E12" s="31" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
-      <c r="G12" s="31" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="H12" s="31" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="I12" s="31" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="K12" s="31" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28.9" customHeight="1" s="28">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>研究開発費比率（R&amp;D/売上高） (%)</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C13" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D13" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E13" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G13" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H13" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I13" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J13" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K13" s="31" t="n">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="14" ht="22.9" customHeight="1" s="28" thickBot="1">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>ROE三分解：売上高純利益率 (%)</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="C14" s="31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G14" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I14" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J14" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="K14" s="31" t="n">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1" s="28">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>ROE三分解：財務レバレッジ (倍)</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C15" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E15" s="31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F15" s="31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G15" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H15" s="31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I15" s="31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J15" s="31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K15" s="31" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="16" ht="27" customHeight="1" s="28">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>投下資本利益率（ROIC） (%)</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G16" s="31" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H16" s="31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I16" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J16" s="31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="K16" s="31" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="17" ht="28.9" customHeight="1" s="28"/>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>※ WACC仮置き: 7.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="13.5" customHeight="1" s="28" thickBot="1"/>
+    </row>
+    <row r="19" ht="13.5" customHeight="1" s="28" thickBot="1">
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="26" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="20" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>その他はR&amp;D/売上高、営業CFなど</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1588,229 +1325,229 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="28" min="1" max="1"/>
-    <col width="10" customWidth="1" style="28" min="2" max="2"/>
-    <col width="10" customWidth="1" style="28" min="3" max="3"/>
-    <col width="10" customWidth="1" style="28" min="4" max="4"/>
-    <col width="10" customWidth="1" style="28" min="5" max="5"/>
-    <col width="10" customWidth="1" style="28" min="6" max="6"/>
-    <col width="10" customWidth="1" style="28" min="7" max="7"/>
-    <col width="10" customWidth="1" style="28" min="8" max="8"/>
-    <col width="10" customWidth="1" style="28" min="9" max="9"/>
-    <col width="10" customWidth="1" style="28" min="10" max="10"/>
-    <col width="10" customWidth="1" style="28" min="11" max="11"/>
+    <col width="32" customWidth="1" style="28" min="1" max="1"/>
+    <col width="12" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="12" customWidth="1" style="28" min="4" max="4"/>
+    <col width="12" customWidth="1" style="28" min="5" max="5"/>
+    <col width="12" customWidth="1" style="28" min="6" max="6"/>
+    <col width="12" customWidth="1" style="28" min="7" max="7"/>
+    <col width="12" customWidth="1" style="28" min="8" max="8"/>
+    <col width="12" customWidth="1" style="28" min="9" max="9"/>
+    <col width="12" customWidth="1" style="28" min="10" max="10"/>
+    <col width="12" customWidth="1" style="28" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>2014年3月期</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>2015年3月期</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>2016年3月期</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>2017年3月期</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>2018年3月期</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="33" t="inlineStr">
         <is>
           <t>2019年3月期</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="33" t="inlineStr">
         <is>
           <t>2020年3月期</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="33" t="inlineStr">
         <is>
           <t>2021年3月期</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="33" t="inlineStr">
         <is>
           <t>2022年3月期</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="33" t="inlineStr">
         <is>
           <t>2023年3月期</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>売上高 (億円)</t>
         </is>
       </c>
-      <c r="B2" s="31" t="n">
+      <c r="B2" s="35" t="n">
         <v>272000</v>
       </c>
-      <c r="C2" s="31" t="n">
+      <c r="C2" s="35" t="n">
         <v>282000</v>
       </c>
-      <c r="D2" s="31" t="n">
+      <c r="D2" s="35" t="n">
         <v>274000</v>
       </c>
-      <c r="E2" s="31" t="n">
+      <c r="E2" s="35" t="n">
         <v>293000</v>
       </c>
-      <c r="F2" s="31" t="n">
+      <c r="F2" s="35" t="n">
         <v>296000</v>
       </c>
-      <c r="G2" s="31" t="n">
+      <c r="G2" s="35" t="n">
         <v>302000</v>
       </c>
-      <c r="H2" s="31" t="n">
+      <c r="H2" s="35" t="n">
         <v>279000</v>
       </c>
-      <c r="I2" s="31" t="n">
+      <c r="I2" s="35" t="n">
         <v>279000</v>
       </c>
-      <c r="J2" s="31" t="n">
+      <c r="J2" s="35" t="n">
         <v>370000</v>
       </c>
-      <c r="K2" s="31" t="n">
+      <c r="K2" s="35" t="n">
         <v>439000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>営業利益 (億円)</t>
         </is>
       </c>
-      <c r="B3" s="31" t="n">
+      <c r="B3" s="35" t="n">
         <v>22320</v>
       </c>
-      <c r="C3" s="31" t="n">
+      <c r="C3" s="35" t="n">
         <v>22850</v>
       </c>
-      <c r="D3" s="31" t="n">
+      <c r="D3" s="35" t="n">
         <v>17820</v>
       </c>
-      <c r="E3" s="31" t="n">
+      <c r="E3" s="35" t="n">
         <v>19080</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="35" t="n">
         <v>22200</v>
       </c>
-      <c r="G3" s="31" t="n">
+      <c r="G3" s="35" t="n">
         <v>21440</v>
       </c>
-      <c r="H3" s="31" t="n">
+      <c r="H3" s="35" t="n">
         <v>8100</v>
       </c>
-      <c r="I3" s="31" t="n">
+      <c r="I3" s="35" t="n">
         <v>22360</v>
       </c>
-      <c r="J3" s="31" t="n">
+      <c r="J3" s="35" t="n">
         <v>36280</v>
       </c>
-      <c r="K3" s="31" t="n">
+      <c r="K3" s="35" t="n">
         <v>32476</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>当期純利益 (億円)</t>
         </is>
       </c>
-      <c r="B4" s="31" t="n">
+      <c r="B4" s="35" t="n">
         <v>19040</v>
       </c>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="35" t="n">
         <v>20780</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="35" t="n">
         <v>14945</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="35" t="n">
         <v>19492</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="35" t="n">
         <v>18953</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="35" t="n">
         <v>20131</v>
       </c>
-      <c r="H4" s="31" t="n">
+      <c r="H4" s="35" t="n">
         <v>8769</v>
       </c>
-      <c r="I4" s="31" t="n">
+      <c r="I4" s="35" t="n">
         <v>22792</v>
       </c>
-      <c r="J4" s="31" t="n">
+      <c r="J4" s="35" t="n">
         <v>28498</v>
       </c>
-      <c r="K4" s="31" t="n">
+      <c r="K4" s="35" t="n">
         <v>34808</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>支払利息 (億円)</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="n">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="n">
         <v>425</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="35" t="n">
         <v>447</v>
       </c>
-      <c r="H5" s="31" t="n">
+      <c r="H5" s="35" t="n">
         <v>499</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="35" t="n">
         <v>494</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="35" t="n">
         <v>574</v>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="35" t="n">
         <v>807</v>
       </c>
     </row>
@@ -1828,192 +1565,192 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="28" min="1" max="1"/>
-    <col width="10" customWidth="1" style="28" min="2" max="2"/>
-    <col width="10" customWidth="1" style="28" min="3" max="3"/>
-    <col width="10" customWidth="1" style="28" min="4" max="4"/>
-    <col width="10" customWidth="1" style="28" min="5" max="5"/>
-    <col width="10" customWidth="1" style="28" min="6" max="6"/>
-    <col width="10" customWidth="1" style="28" min="7" max="7"/>
-    <col width="10" customWidth="1" style="28" min="8" max="8"/>
-    <col width="10" customWidth="1" style="28" min="9" max="9"/>
-    <col width="10" customWidth="1" style="28" min="10" max="10"/>
-    <col width="10" customWidth="1" style="28" min="11" max="11"/>
+    <col width="32" customWidth="1" style="28" min="1" max="1"/>
+    <col width="12" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="12" customWidth="1" style="28" min="4" max="4"/>
+    <col width="12" customWidth="1" style="28" min="5" max="5"/>
+    <col width="12" customWidth="1" style="28" min="6" max="6"/>
+    <col width="12" customWidth="1" style="28" min="7" max="7"/>
+    <col width="12" customWidth="1" style="28" min="8" max="8"/>
+    <col width="12" customWidth="1" style="28" min="9" max="9"/>
+    <col width="12" customWidth="1" style="28" min="10" max="10"/>
+    <col width="12" customWidth="1" style="28" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>2014年3月期</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>2015年3月期</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>2016年3月期</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>2017年3月期</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>2018年3月期</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="33" t="inlineStr">
         <is>
           <t>2019年3月期</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="33" t="inlineStr">
         <is>
           <t>2020年3月期</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="33" t="inlineStr">
         <is>
           <t>2021年3月期</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="33" t="inlineStr">
         <is>
           <t>2022年3月期</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="33" t="inlineStr">
         <is>
           <t>2023年3月期</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>資産合計 (億円)</t>
         </is>
       </c>
-      <c r="B2" s="31" t="n">
+      <c r="B2" s="35" t="n">
         <v>468000</v>
       </c>
-      <c r="C2" s="31" t="n">
+      <c r="C2" s="35" t="n">
         <v>491000</v>
       </c>
-      <c r="D2" s="31" t="n">
+      <c r="D2" s="35" t="n">
         <v>494000</v>
       </c>
-      <c r="E2" s="31" t="n">
+      <c r="E2" s="35" t="n">
         <v>499000</v>
       </c>
-      <c r="F2" s="31" t="n">
+      <c r="F2" s="35" t="n">
         <v>528000</v>
       </c>
-      <c r="G2" s="31" t="n">
+      <c r="G2" s="35" t="n">
         <v>552000</v>
       </c>
-      <c r="H2" s="31" t="n">
+      <c r="H2" s="35" t="n">
         <v>571000</v>
       </c>
-      <c r="I2" s="31" t="n">
+      <c r="I2" s="35" t="n">
         <v>619000</v>
       </c>
-      <c r="J2" s="31" t="n">
+      <c r="J2" s="35" t="n">
         <v>675000</v>
       </c>
-      <c r="K2" s="31" t="n">
+      <c r="K2" s="35" t="n">
         <v>808000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>純資産合計（株主資本） (億円)</t>
         </is>
       </c>
-      <c r="B3" s="31" t="n">
+      <c r="B3" s="35" t="n">
         <v>168000</v>
       </c>
-      <c r="C3" s="31" t="n">
+      <c r="C3" s="35" t="n">
         <v>182000</v>
       </c>
-      <c r="D3" s="31" t="n">
+      <c r="D3" s="35" t="n">
         <v>190000</v>
       </c>
-      <c r="E3" s="31" t="n">
+      <c r="E3" s="35" t="n">
         <v>196000</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="35" t="n">
         <v>210000</v>
       </c>
-      <c r="G3" s="31" t="n">
+      <c r="G3" s="35" t="n">
         <v>210000</v>
       </c>
-      <c r="H3" s="31" t="n">
+      <c r="H3" s="35" t="n">
         <v>219000</v>
       </c>
-      <c r="I3" s="31" t="n">
+      <c r="I3" s="35" t="n">
         <v>231000</v>
       </c>
-      <c r="J3" s="31" t="n">
+      <c r="J3" s="35" t="n">
         <v>262000</v>
       </c>
-      <c r="K3" s="31" t="n">
+      <c r="K3" s="35" t="n">
         <v>311000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>純有利子負債 (億円)</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="n">
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="n">
         <v>-12000</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="35" t="n">
         <v>-18000</v>
       </c>
-      <c r="H4" s="31" t="n">
+      <c r="H4" s="35" t="n">
         <v>-15000</v>
       </c>
-      <c r="I4" s="31" t="n">
+      <c r="I4" s="35" t="n">
         <v>-23000</v>
       </c>
-      <c r="J4" s="31" t="n">
+      <c r="J4" s="35" t="n">
         <v>-38000</v>
       </c>
-      <c r="K4" s="31" t="n">
+      <c r="K4" s="35" t="n">
         <v>-52000</v>
       </c>
     </row>
@@ -2031,221 +1768,221 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="28" min="1" max="1"/>
-    <col width="10" customWidth="1" style="28" min="2" max="2"/>
-    <col width="10" customWidth="1" style="28" min="3" max="3"/>
-    <col width="10" customWidth="1" style="28" min="4" max="4"/>
-    <col width="10" customWidth="1" style="28" min="5" max="5"/>
-    <col width="10" customWidth="1" style="28" min="6" max="6"/>
-    <col width="10" customWidth="1" style="28" min="7" max="7"/>
-    <col width="10" customWidth="1" style="28" min="8" max="8"/>
-    <col width="10" customWidth="1" style="28" min="9" max="9"/>
-    <col width="10" customWidth="1" style="28" min="10" max="10"/>
-    <col width="10" customWidth="1" style="28" min="11" max="11"/>
+    <col width="32" customWidth="1" style="28" min="1" max="1"/>
+    <col width="12" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="12" customWidth="1" style="28" min="4" max="4"/>
+    <col width="12" customWidth="1" style="28" min="5" max="5"/>
+    <col width="12" customWidth="1" style="28" min="6" max="6"/>
+    <col width="12" customWidth="1" style="28" min="7" max="7"/>
+    <col width="12" customWidth="1" style="28" min="8" max="8"/>
+    <col width="12" customWidth="1" style="28" min="9" max="9"/>
+    <col width="12" customWidth="1" style="28" min="10" max="10"/>
+    <col width="12" customWidth="1" style="28" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>2014年3月期</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>2015年3月期</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>2016年3月期</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>2017年3月期</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>2018年3月期</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="33" t="inlineStr">
         <is>
           <t>2019年3月期</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="33" t="inlineStr">
         <is>
           <t>2020年3月期</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="33" t="inlineStr">
         <is>
           <t>2021年3月期</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="33" t="inlineStr">
         <is>
           <t>2022年3月期</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="33" t="inlineStr">
         <is>
           <t>2023年3月期</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>営業活動によるキャッシュ・フロー (億円)</t>
         </is>
       </c>
-      <c r="B2" s="31" t="n">
+      <c r="B2" s="35" t="n">
         <v>26500</v>
       </c>
-      <c r="C2" s="31" t="n">
+      <c r="C2" s="35" t="n">
         <v>27800</v>
       </c>
-      <c r="D2" s="31" t="n">
+      <c r="D2" s="35" t="n">
         <v>24100</v>
       </c>
-      <c r="E2" s="31" t="n">
+      <c r="E2" s="35" t="n">
         <v>23200</v>
       </c>
-      <c r="F2" s="31" t="n">
+      <c r="F2" s="35" t="n">
         <v>27700</v>
       </c>
-      <c r="G2" s="31" t="n">
+      <c r="G2" s="35" t="n">
         <v>25900</v>
       </c>
-      <c r="H2" s="31" t="n">
+      <c r="H2" s="35" t="n">
         <v>19200</v>
       </c>
-      <c r="I2" s="31" t="n">
+      <c r="I2" s="35" t="n">
         <v>30700</v>
       </c>
-      <c r="J2" s="31" t="n">
+      <c r="J2" s="35" t="n">
         <v>44800</v>
       </c>
-      <c r="K2" s="31" t="n">
+      <c r="K2" s="35" t="n">
         <v>54800</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>投資活動によるキャッシュ・フロー (億円)</t>
         </is>
       </c>
-      <c r="B3" s="31" t="n">
+      <c r="B3" s="35" t="n">
         <v>-22100</v>
       </c>
-      <c r="C3" s="31" t="n">
+      <c r="C3" s="35" t="n">
         <v>-24300</v>
       </c>
-      <c r="D3" s="31" t="n">
+      <c r="D3" s="35" t="n">
         <v>-21500</v>
       </c>
-      <c r="E3" s="31" t="n">
+      <c r="E3" s="35" t="n">
         <v>-19800</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="35" t="n">
         <v>-22100</v>
       </c>
-      <c r="G3" s="31" t="n">
+      <c r="G3" s="35" t="n">
         <v>-24500</v>
       </c>
-      <c r="H3" s="31" t="n">
+      <c r="H3" s="35" t="n">
         <v>-20100</v>
       </c>
-      <c r="I3" s="31" t="n">
+      <c r="I3" s="35" t="n">
         <v>-22300</v>
       </c>
-      <c r="J3" s="31" t="n">
+      <c r="J3" s="35" t="n">
         <v>-28200</v>
       </c>
-      <c r="K3" s="31" t="n">
+      <c r="K3" s="35" t="n">
         <v>-36200</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>財務活動によるキャッシュ・フロー (億円)</t>
         </is>
       </c>
-      <c r="B4" s="31" t="n">
+      <c r="B4" s="35" t="n">
         <v>-4200</v>
       </c>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="35" t="n">
         <v>-3200</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="35" t="n">
         <v>-2800</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="35" t="n">
         <v>-3100</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="35" t="n">
         <v>-5200</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="35" t="n">
         <v>-4800</v>
       </c>
-      <c r="H4" s="31" t="n">
+      <c r="H4" s="35" t="n">
         <v>-3100</v>
       </c>
-      <c r="I4" s="31" t="n">
+      <c r="I4" s="35" t="n">
         <v>-7100</v>
       </c>
-      <c r="J4" s="31" t="n">
+      <c r="J4" s="35" t="n">
         <v>-14100</v>
       </c>
-      <c r="K4" s="31" t="n">
+      <c r="K4" s="35" t="n">
         <v>-19800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>フリー・キャッシュ・フロー (億円)</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="35" t="n">
         <v>4400</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="35" t="n">
         <v>3500</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="35" t="n">
         <v>2600</v>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="35" t="n">
         <v>3400</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="35" t="n">
         <v>5600</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="35" t="n">
         <v>1400</v>
       </c>
-      <c r="H5" s="31" t="n">
+      <c r="H5" s="35" t="n">
         <v>-900</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="35" t="n">
         <v>8400</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="35" t="n">
         <v>16600</v>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="35" t="n">
         <v>18600</v>
       </c>
     </row>
@@ -2264,448 +2001,448 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="28" min="1" max="1"/>
-    <col width="14" customWidth="1" style="28" min="2" max="2"/>
-    <col width="10" customWidth="1" style="28" min="3" max="3"/>
-    <col width="10" customWidth="1" style="28" min="4" max="4"/>
-    <col width="10" customWidth="1" style="28" min="5" max="5"/>
-    <col width="10" customWidth="1" style="28" min="6" max="6"/>
-    <col width="10" customWidth="1" style="28" min="7" max="7"/>
-    <col width="10" customWidth="1" style="28" min="8" max="8"/>
-    <col width="10" customWidth="1" style="28" min="9" max="9"/>
-    <col width="10" customWidth="1" style="28" min="10" max="10"/>
-    <col width="10" customWidth="1" style="28" min="11" max="11"/>
-    <col width="10" customWidth="1" style="28" min="12" max="12"/>
+    <col width="12" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="12" customWidth="1" style="28" min="4" max="4"/>
+    <col width="12" customWidth="1" style="28" min="5" max="5"/>
+    <col width="12" customWidth="1" style="28" min="6" max="6"/>
+    <col width="12" customWidth="1" style="28" min="7" max="7"/>
+    <col width="12" customWidth="1" style="28" min="8" max="8"/>
+    <col width="12" customWidth="1" style="28" min="9" max="9"/>
+    <col width="12" customWidth="1" style="28" min="10" max="10"/>
+    <col width="12" customWidth="1" style="28" min="11" max="11"/>
+    <col width="12" customWidth="1" style="28" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>セグメント</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>2014年3月期</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>2015年3月期</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>2016年3月期</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>2017年3月期</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="33" t="inlineStr">
         <is>
           <t>2018年3月期</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="33" t="inlineStr">
         <is>
           <t>2019年3月期</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="33" t="inlineStr">
         <is>
           <t>2020年3月期</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="33" t="inlineStr">
         <is>
           <t>2021年3月期</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="33" t="inlineStr">
         <is>
           <t>2022年3月期</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="33" t="inlineStr">
         <is>
           <t>2023年3月期</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
-        <is>
-          <t>売上(億)</t>
-        </is>
-      </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K2" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="31" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>売上高(億)</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>利益(億)</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="31" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>北米</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
-        <is>
-          <t>売上(億)</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="31" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>売上高(億)</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>北米</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>利益(億)</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="31" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>アジア</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>売上(億)</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="31" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>売上高(億)</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>アジア</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>利益(億)</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="31" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2725,135 +2462,135 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="28" min="1" max="1"/>
-    <col width="16" customWidth="1" style="28" min="2" max="2"/>
-    <col width="16" customWidth="1" style="28" min="3" max="3"/>
-    <col width="16" customWidth="1" style="28" min="4" max="4"/>
-    <col width="16" customWidth="1" style="28" min="5" max="5"/>
-    <col width="16" customWidth="1" style="28" min="6" max="6"/>
+    <col width="20" customWidth="1" style="28" min="1" max="1"/>
+    <col width="20" customWidth="1" style="28" min="2" max="2"/>
+    <col width="20" customWidth="1" style="28" min="3" max="3"/>
+    <col width="20" customWidth="1" style="28" min="4" max="4"/>
+    <col width="20" customWidth="1" style="28" min="5" max="5"/>
+    <col width="20" customWidth="1" style="28" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>企業名</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>自己資本利益率ROE(%)</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>投下資本利益率ROIC(%)</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>株価純資産倍率PBR(倍)</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>EV/EBITDA(倍)</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>売上高営業利益率(%)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>ホンダ</t>
         </is>
       </c>
-      <c r="B2" s="31" t="n">
+      <c r="B2" s="35" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="C2" s="31" t="n">
+      <c r="C2" s="35" t="n">
         <v>6.1</v>
       </c>
-      <c r="D2" s="31" t="n">
+      <c r="D2" s="35" t="n">
         <v>0.7</v>
       </c>
-      <c r="E2" s="31" t="n">
+      <c r="E2" s="35" t="n">
         <v>4.2</v>
       </c>
-      <c r="F2" s="31" t="n">
+      <c r="F2" s="35" t="n">
         <v>3.1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>日産</t>
         </is>
       </c>
-      <c r="B3" s="31" t="n">
+      <c r="B3" s="35" t="n">
         <v>-15</v>
       </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="n">
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n">
         <v>0.4</v>
       </c>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="31" t="n">
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="n">
         <v>-1.2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>フォード</t>
         </is>
       </c>
-      <c r="B4" s="31" t="n">
+      <c r="B4" s="35" t="n">
         <v>9.1</v>
       </c>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="35" t="n">
         <v>5.8</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="35" t="n">
         <v>1.1</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="35" t="n">
         <v>6.1</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="35" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="35" t="n">
         <v>18.2</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="35" t="n">
         <v>9.1</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="35" t="n">
         <v>1.2</v>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="35" t="n">
         <v>5.2</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="35" t="n">
         <v>6.9</v>
       </c>
     </row>
